--- a/data/trans_bre/IP25-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP25-Estudios-trans_bre.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,8 +515,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,15 +531,13 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Brecha de género relativa</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -563,27 +559,17 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -596,8 +582,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -627,27 +611,17 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>-0,67%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,67%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
           <t>-6,13%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -660,42 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 10,17</t>
+          <t>-2,63; 11,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 5,07</t>
+          <t>-6,4; 5,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 1,0</t>
+          <t>-14,2; 0,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,8; 13,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 11,98</t>
+          <t>-6,65; 5,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 5,59</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-14,01; 0,82</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-14,77; 1,01</t>
         </is>
       </c>
     </row>
@@ -727,27 +691,17 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>-4,16%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-4,16%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
           <t>-1,45%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -760,42 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 5,48</t>
+          <t>-1,11; 5,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,82; -0,68</t>
+          <t>-6,9; -0,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 1,38</t>
+          <t>-4,08; 1,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,21; 6,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 6,27</t>
+          <t>-7,39; -0,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,36; -0,75</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-4,65; 1,5</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-4,39; 1,88</t>
         </is>
       </c>
     </row>
@@ -827,27 +771,17 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
           <t>-0,55%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -860,42 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 11,15</t>
+          <t>-2,48; 10,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 7,48</t>
+          <t>-3,89; 7,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 5,88</t>
+          <t>-6,69; 5,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,82; 13,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 14,26</t>
+          <t>-4,34; 9,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 8,83</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-7,0; 6,97</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-7,4; 6,69</t>
         </is>
       </c>
     </row>
@@ -927,27 +851,17 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>-2,37%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-2,37%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
           <t>-1,64%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -960,42 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,37</t>
+          <t>0,43; 5,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 0,4</t>
+          <t>-4,41; 0,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 1,09</t>
+          <t>-4,04; 0,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,49; 6,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,23</t>
+          <t>-4,81; 0,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 0,44</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-4,17; 1,21</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-4,39; 1,03</t>
         </is>
       </c>
     </row>
@@ -1008,11 +912,11 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
   </mergeCells>

--- a/data/trans_bre/IP25-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP25-Estudios-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 11,63</t>
+          <t>-3,04; 10,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 5,15</t>
+          <t>-6,44; 5,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 0,93</t>
+          <t>-14,73; 1,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 13,96</t>
+          <t>-3,34; 12,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 5,59</t>
+          <t>-6,66; 5,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 1,01</t>
+          <t>-15,3; 1,08</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 5,72</t>
+          <t>-0,56; 5,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,9; -0,82</t>
+          <t>-7,09; -0,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 1,7</t>
+          <t>-4,41; 1,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 6,63</t>
+          <t>-0,62; 6,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,39; -0,9</t>
+          <t>-7,63; -0,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 1,88</t>
+          <t>-4,69; 1,33</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 10,84</t>
+          <t>-2,2; 10,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 7,93</t>
+          <t>-3,9; 7,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 5,49</t>
+          <t>-6,46; 5,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 13,71</t>
+          <t>-2,52; 13,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 9,3</t>
+          <t>-4,27; 8,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 6,69</t>
+          <t>-7,28; 6,53</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 5,38</t>
+          <t>0,27; 5,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 0,55</t>
+          <t>-4,6; 0,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 0,93</t>
+          <t>-3,92; 1,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 6,31</t>
+          <t>0,3; 6,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 0,61</t>
+          <t>-4,99; 0,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 1,03</t>
+          <t>-4,27; 1,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP25-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP25-Estudios-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 10,49</t>
+          <t>-2,85; 10,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 5,0</t>
+          <t>-6,96; 5,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,73; 1,02</t>
+          <t>-13,48; 1,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 12,32</t>
+          <t>-3,04; 11,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 5,48</t>
+          <t>-7,26; 5,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,3; 1,08</t>
+          <t>-14,01; 0,82</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 5,61</t>
+          <t>-1,22; 5,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,09; -0,64</t>
+          <t>-6,82; -0,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 1,2</t>
+          <t>-4,34; 1,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 6,47</t>
+          <t>-1,27; 6,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,63; -0,69</t>
+          <t>-7,36; -0,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 1,33</t>
+          <t>-4,65; 1,5</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 10,6</t>
+          <t>-1,73; 11,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 7,14</t>
+          <t>-3,79; 7,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 5,36</t>
+          <t>-6,26; 5,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 13,37</t>
+          <t>-2,01; 14,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 8,39</t>
+          <t>-4,14; 8,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 6,53</t>
+          <t>-7,0; 6,97</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 5,68</t>
+          <t>0,5; 5,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 0,45</t>
+          <t>-4,75; 0,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 1,03</t>
+          <t>-3,84; 1,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 6,57</t>
+          <t>0,57; 6,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 0,51</t>
+          <t>-5,1; 0,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 1,15</t>
+          <t>-4,17; 1,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP25-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP25-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3,72</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,63</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-5,83</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,67%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-6,13%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>3.717510017894254</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.631474662141307</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-5.832265051677776</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.0416675158297187</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.006683782563861788</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.06132589460326965</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-2,85; 10,17</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-6,96; 5,07</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-13,48; 1,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-3,04; 11,98</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-7,26; 5,59</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-14,01; 0,82</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-2.845848579666653</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-6.956774249629001</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-13.47910241969334</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>-0.03041773977578698</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.07257179352120831</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.1401055835074392</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>10.17296799823829</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>5.068741663875435</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.003963302451884</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.1197600369554624</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.05586116407318782</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.008249134184179389</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2,29</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-3,82</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,35</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-4,16%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-1,45%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-1,22; 5,48</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-6,82; -0,68</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-4,34; 1,38</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-1,27; 6,27</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-7,36; -0,75</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-4,65; 1,5</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>2.294841367564193</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-3.82362902724549</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-1.345590412935005</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.02585562896768386</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.041638509825155</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.01453788033015711</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>4,28</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,38</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,48</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,16%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-0,55%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.22190411789235</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-6.823540615048584</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-4.344988601963347</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.01270545968927019</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.07361335393664162</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.04648556361958663</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-1,73; 11,15</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,79; 7,48</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-6,26; 5,88</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-2,01; 14,26</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-4,14; 8,83</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-7,0; 6,97</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5.480308296611831</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>-0.6808353054559871</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.380633561762315</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.062691824607265</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-0.007513013169117221</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.01498021486666919</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,77 +767,161 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2,79</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-2,17</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,49</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-2,37%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-1,64%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>4.277317899243894</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.38375942459158</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.4811412393083914</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.05160932256144321</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.01572975380123363</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.005548109669455578</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,5; 5,37</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-4,75; 0,4</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-3,84; 1,09</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,57; 6,23</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-5,1; 0,44</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-4,17; 1,21</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-1.731747775905096</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.790775114015319</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-6.261487791089356</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-0.02005291036358799</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.04137253836463732</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.07001733288400294</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>11.15338581746919</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.481584521760714</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.880136686593289</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.14261461963008</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.08825661437371186</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.06972762504519225</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>2.789280147426676</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-2.165722258727087</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-1.493617665982028</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.03186864444257796</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.02373459330950238</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.01635533306248851</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.5042521080540632</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.747783349934489</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.836271919237275</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>0.00573497262866174</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.05101540476112192</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.04166839330405903</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.366363809935047</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.3959273744307487</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.086920194524964</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.06227551781577886</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.004398222521339105</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.01207351016952813</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -913,12 +930,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
